--- a/output/laminas_comunales/comunal_p_basica_a_2021_arica_y_parinacota.xlsx
+++ b/output/laminas_comunales/comunal_p_basica_a_2021_arica_y_parinacota.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,7 +384,622 @@
         </is>
       </c>
       <c r="C2">
+        <v>139450.890625</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>139391.484375</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>131465.3125</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>131418.875</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>127970.7265625</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>127816.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>127248.5546875</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>127002.5625</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>125519.3984375</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>125374.2421875</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>123275.8359375</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>122938.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>116167.9609375</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>115903.078125</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>50.7129325866699</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>50.6774024963379</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>49.5954132080078</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>49.5587005615234</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>49.4841079711914</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>49.4108695983887</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>46.902515411377</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>46.8801116943359</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>44.4791107177734</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>44.4306755065918</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>43.9545288085938</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>43.8107223510742</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>43.7684288024902</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>43.7294883728027</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>18.4125690460205</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>18.1748104095459</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>17.5853462219238</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>17.3297367095947</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>15.2604446411133</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>14.9662675857544</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>13.4952812194824</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C37">
         <v>13.3008241653442</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>13.1104097366333</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>12.9473419189453</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>10.0157260894775</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>9.905519485473629</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>7.71615552902222</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>7.55574178695679</v>
       </c>
     </row>
   </sheetData>
